--- a/sorting_results.xlsx
+++ b/sorting_results.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Crys\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Crys\Desktop\hhkl\ИгслуеSort\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -188,7 +188,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -368,6 +368,12 @@
         <bgColor indexed="65"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="10">
     <border>
@@ -529,9 +535,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -621,11 +628,10 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -658,27 +664,41 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="22225" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
-              <a:round/>
             </a:ln>
-            <a:effectLst/>
+            <a:effectLst>
+              <a:glow rad="139700">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="14000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
-            <c:size val="5"/>
+            <c:size val="3"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
               </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:glow rad="63500">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="175000"/>
+                    <a:alpha val="25000"/>
+                  </a:schemeClr>
+                </a:glow>
+              </a:effectLst>
             </c:spPr>
           </c:marker>
           <c:xVal>
@@ -1142,9 +1162,10 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                  <a:alpha val="75000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -1160,9 +1181,8 @@
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="50000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
@@ -1176,9 +1196,8 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -1204,9 +1223,10 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                  <a:alpha val="75000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -1222,9 +1242,8 @@
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="50000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
@@ -1238,9 +1257,8 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -1269,11 +1287,14 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
+        <a:schemeClr val="dk1">
           <a:lumMod val="15000"/>
           <a:lumOff val="85000"/>
         </a:schemeClr>
@@ -1329,11 +1350,10 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+            <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:latin typeface="+mn-lt"/>
@@ -1366,27 +1386,41 @@
             </c:strRef>
           </c:tx>
           <c:spPr>
-            <a:ln w="19050" cap="rnd">
+            <a:ln w="22225" cap="rnd">
               <a:solidFill>
                 <a:schemeClr val="accent1"/>
               </a:solidFill>
-              <a:round/>
             </a:ln>
-            <a:effectLst/>
+            <a:effectLst>
+              <a:glow rad="139700">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="175000"/>
+                  <a:alpha val="14000"/>
+                </a:schemeClr>
+              </a:glow>
+            </a:effectLst>
           </c:spPr>
           <c:marker>
             <c:symbol val="circle"/>
-            <c:size val="5"/>
+            <c:size val="3"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
               </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
+              <a:ln>
+                <a:noFill/>
               </a:ln>
-              <a:effectLst/>
+              <a:effectLst>
+                <a:glow rad="63500">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="175000"/>
+                    <a:alpha val="25000"/>
+                  </a:schemeClr>
+                </a:glow>
+              </a:effectLst>
             </c:spPr>
           </c:marker>
           <c:xVal>
@@ -1850,9 +1884,10 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                  <a:alpha val="75000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -1868,9 +1903,8 @@
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="50000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
@@ -1884,9 +1918,8 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -1912,9 +1945,10 @@
           <c:spPr>
             <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
+                <a:schemeClr val="dk1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                  <a:alpha val="75000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -1930,9 +1964,8 @@
           <a:noFill/>
           <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
             <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="25000"/>
-                <a:lumOff val="75000"/>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="50000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
@@ -1946,9 +1979,8 @@
             <a:pPr>
               <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="75000"/>
                   </a:schemeClr>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
@@ -1977,11 +2009,14 @@
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:schemeClr val="bg1"/>
+      <a:schemeClr val="dk1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
     </a:solidFill>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
       <a:solidFill>
-        <a:schemeClr val="tx1">
+        <a:schemeClr val="dk1">
           <a:lumMod val="15000"/>
           <a:lumOff val="85000"/>
         </a:schemeClr>
@@ -2089,56 +2124,46 @@
 </file>
 
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="245">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
   </cs:axisTitle>
   <cs:categoryAxis>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+  <cs:chartArea>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="bg1"/>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
       </a:solidFill>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="dk1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
@@ -2146,16 +2171,15 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
+      <a:schemeClr val="lt1">
         <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -2165,23 +2189,18 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="15000"/>
+        <a:lumOff val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="lt1"/>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
       </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
     <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
@@ -2189,63 +2208,123 @@
     </cs:bodyPr>
   </cs:dataLabelCallout>
   <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:effectRef idx="0">
       <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050" cap="rnd">
+      <a:ln w="22225" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:round/>
       </a:ln>
+      <a:effectLst>
+        <a:glow rad="139700">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="14000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
     </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:lumMod val="60000"/>
+          <a:lumOff val="40000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="3"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
@@ -2269,31 +2348,349 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:noFill/>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+            <a:alpha val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="1" kern="1200" cap="none" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
+    <cs:bodyPr/>
+  </cs:valueAxis>
+  <cs:wall>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="245">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
@@ -2304,78 +2701,7 @@
       </a:solidFill>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="dk1">
             <a:lumMod val="15000"/>
             <a:lumOff val="85000"/>
           </a:schemeClr>
@@ -2383,295 +2709,15 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
+      <a:schemeClr val="lt1">
         <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -2681,23 +2727,18 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="15000"/>
+        <a:lumOff val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="lt1"/>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
       </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
     <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
@@ -2705,63 +2746,123 @@
     </cs:bodyPr>
   </cs:dataLabelCallout>
   <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
+    <cs:effectRef idx="0">
       <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:miter lim="800000"/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050" cap="rnd">
+      <a:ln w="22225" cap="rnd">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:round/>
       </a:ln>
+      <a:effectLst>
+        <a:glow rad="139700">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="14000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
     </cs:spPr>
   </cs:dataPointLine>
   <cs:dataPointMarker>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1">
+    <cs:fillRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:lumMod val="60000"/>
+          <a:lumOff val="40000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:effectLst>
+        <a:glow rad="63500">
+          <a:schemeClr val="phClr">
+            <a:satMod val="175000"/>
+            <a:alpha val="25000"/>
+          </a:schemeClr>
+        </a:glow>
+      </a:effectLst>
     </cs:spPr>
   </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointMarkerLayout symbol="circle" size="3"/>
   <cs:dataPointWireframe>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
@@ -2785,21 +2886,18 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
@@ -2809,20 +2907,19 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
+          <a:lumMod val="50000"/>
+          <a:lumOff val="50000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="75000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -2834,14 +2931,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -2853,14 +2949,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -2872,14 +2967,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
   </cs:floor>
   <cs:gridlineMajor>
     <cs:lnRef idx="0"/>
@@ -2891,9 +2980,10 @@
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+            <a:alpha val="75000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -2910,9 +3000,10 @@
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+            <a:alpha val="25000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -2924,14 +3015,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
+          <a:schemeClr val="lt1">
             <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -2943,14 +3033,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -2962,27 +3051,26 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+  <cs:plotArea>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+  <cs:plotArea3D>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
   </cs:plotArea3D>
   <cs:seriesAxis>
@@ -2990,9 +3078,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -3002,14 +3089,13 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -3021,12 +3107,11 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+    <cs:defRPr sz="1400" b="1" kern="1200" cap="none" baseline="0"/>
   </cs:title>
   <cs:trendline>
     <cs:lnRef idx="0">
@@ -3035,14 +3120,15 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="lt1"/>
     </cs:fontRef>
     <cs:spPr>
-      <a:ln w="19050" cap="rnd">
+      <a:ln w="25400" cap="rnd">
         <a:solidFill>
-          <a:schemeClr val="phClr"/>
+          <a:schemeClr val="phClr">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
         </a:solidFill>
-        <a:prstDash val="sysDot"/>
       </a:ln>
     </cs:spPr>
   </cs:trendline>
@@ -3051,9 +3137,8 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:defRPr sz="900" kern="1200"/>
@@ -3063,17 +3148,18 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
+      <a:schemeClr val="dk1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
-        <a:schemeClr val="lt1"/>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="85000"/>
+        </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:ln w="9525">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -3085,37 +3171,30 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
+      <a:schemeClr val="lt1">
+        <a:lumMod val="75000"/>
       </a:schemeClr>
     </cs:fontRef>
     <cs:spPr>
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
       </a:ln>
     </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr/>
   </cs:valueAxis>
   <cs:wall>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
   </cs:wall>
 </cs:chartStyle>
 </file>
@@ -3448,786 +3527,1307 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C70"/>
+  <dimension ref="A1:P70"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.08984375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7265625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.1796875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.7265625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="15" style="2" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A2" s="1">
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A2" s="2">
         <v>100</v>
       </c>
-      <c r="B2" s="1">
+      <c r="B2" s="2">
         <v>2984</v>
       </c>
-      <c r="C2" s="1">
+      <c r="C2" s="2">
         <v>300</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A3" s="1">
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A3" s="2">
         <v>1569</v>
       </c>
-      <c r="B3" s="1">
+      <c r="B3" s="2">
         <v>524</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="2">
         <v>4707</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A4" s="1">
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A4" s="2">
         <v>3038</v>
       </c>
-      <c r="B4" s="1">
+      <c r="B4" s="2">
         <v>932</v>
       </c>
-      <c r="C4" s="1">
+      <c r="C4" s="2">
         <v>9114</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="1">
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A5" s="2">
         <v>4507</v>
       </c>
-      <c r="B5" s="1">
+      <c r="B5" s="2">
         <v>1302</v>
       </c>
-      <c r="C5" s="1">
+      <c r="C5" s="2">
         <v>13521</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="1">
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A6" s="2">
         <v>5976</v>
       </c>
-      <c r="B6" s="1">
+      <c r="B6" s="2">
         <v>1736</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="2">
         <v>17928</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="1">
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A7" s="2">
         <v>7445</v>
       </c>
-      <c r="B7" s="1">
+      <c r="B7" s="2">
         <v>2148</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C7" s="2">
         <v>22335</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="1">
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A8" s="2">
         <v>8914</v>
       </c>
-      <c r="B8" s="1">
+      <c r="B8" s="2">
         <v>2586</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C8" s="2">
         <v>26742</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A9" s="1">
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A9" s="2">
         <v>10383</v>
       </c>
-      <c r="B9" s="1">
+      <c r="B9" s="2">
         <v>2982</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C9" s="2">
         <v>31149</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A10" s="1">
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A10" s="2">
         <v>11852</v>
       </c>
-      <c r="B10" s="1">
+      <c r="B10" s="2">
         <v>3838</v>
       </c>
-      <c r="C10" s="1">
+      <c r="C10" s="2">
         <v>35556</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A11" s="1">
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A11" s="2">
         <v>13322</v>
       </c>
-      <c r="B11" s="1">
+      <c r="B11" s="2">
         <v>3987</v>
       </c>
-      <c r="C11" s="1">
+      <c r="C11" s="2">
         <v>39966</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A12" s="1">
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1"/>
+      <c r="P11" s="1"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A12" s="2">
         <v>14791</v>
       </c>
-      <c r="B12" s="1">
+      <c r="B12" s="2">
         <v>4643</v>
       </c>
-      <c r="C12" s="1">
+      <c r="C12" s="2">
         <v>44373</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="1">
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A13" s="2">
         <v>16260</v>
       </c>
-      <c r="B13" s="1">
+      <c r="B13" s="2">
         <v>5185</v>
       </c>
-      <c r="C13" s="1">
+      <c r="C13" s="2">
         <v>48780</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="1">
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A14" s="2">
         <v>17729</v>
       </c>
-      <c r="B14" s="1">
+      <c r="B14" s="2">
         <v>5481</v>
       </c>
-      <c r="C14" s="1">
+      <c r="C14" s="2">
         <v>53187</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A15" s="1">
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A15" s="2">
         <v>19198</v>
       </c>
-      <c r="B15" s="1">
+      <c r="B15" s="2">
         <v>6194</v>
       </c>
-      <c r="C15" s="1">
+      <c r="C15" s="2">
         <v>57594</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="1">
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A16" s="2">
         <v>20667</v>
       </c>
-      <c r="B16" s="1">
+      <c r="B16" s="2">
         <v>6545</v>
       </c>
-      <c r="C16" s="1">
+      <c r="C16" s="2">
         <v>62001</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="1">
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A17" s="2">
         <v>22136</v>
       </c>
-      <c r="B17" s="1">
+      <c r="B17" s="2">
         <v>6624</v>
       </c>
-      <c r="C17" s="1">
+      <c r="C17" s="2">
         <v>66408</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="1">
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A18" s="2">
         <v>23605</v>
       </c>
-      <c r="B18" s="1">
+      <c r="B18" s="2">
         <v>7428</v>
       </c>
-      <c r="C18" s="1">
+      <c r="C18" s="2">
         <v>70815</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" s="1">
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A19" s="2">
         <v>25075</v>
       </c>
-      <c r="B19" s="1">
+      <c r="B19" s="2">
         <v>8010</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C19" s="2">
         <v>75225</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="1">
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A20" s="2">
         <v>26544</v>
       </c>
-      <c r="B20" s="1">
+      <c r="B20" s="2">
         <v>70024</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C20" s="2">
         <v>79632</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" s="1">
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A21" s="2">
         <v>28013</v>
       </c>
-      <c r="B21" s="1">
+      <c r="B21" s="2">
         <v>8342</v>
       </c>
-      <c r="C21" s="1">
+      <c r="C21" s="2">
         <v>84039</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" s="1">
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A22" s="2">
         <v>29482</v>
       </c>
-      <c r="B22" s="1">
+      <c r="B22" s="2">
         <v>9314</v>
       </c>
-      <c r="C22" s="1">
+      <c r="C22" s="2">
         <v>88446</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" s="1">
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A23" s="2">
         <v>30951</v>
       </c>
-      <c r="B23" s="1">
+      <c r="B23" s="2">
         <v>9390</v>
       </c>
-      <c r="C23" s="1">
+      <c r="C23" s="2">
         <v>92853</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" s="1">
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A24" s="2">
         <v>32420</v>
       </c>
-      <c r="B24" s="1">
+      <c r="B24" s="2">
         <v>13326</v>
       </c>
-      <c r="C24" s="1">
+      <c r="C24" s="2">
         <v>97260</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="1">
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A25" s="2">
         <v>33889</v>
       </c>
-      <c r="B25" s="1">
+      <c r="B25" s="2">
         <v>10786</v>
       </c>
-      <c r="C25" s="1">
+      <c r="C25" s="2">
         <v>101667</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="1">
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A26" s="2">
         <v>35358</v>
       </c>
-      <c r="B26" s="1">
+      <c r="B26" s="2">
         <v>14850</v>
       </c>
-      <c r="C26" s="1">
+      <c r="C26" s="2">
         <v>106074</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="1">
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+      <c r="K26" s="1"/>
+      <c r="L26" s="1"/>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A27" s="2">
         <v>36827</v>
       </c>
-      <c r="B27" s="1">
+      <c r="B27" s="2">
         <v>12762</v>
       </c>
-      <c r="C27" s="1">
+      <c r="C27" s="2">
         <v>110481</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="1">
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+      <c r="K27" s="1"/>
+      <c r="L27" s="1"/>
+      <c r="M27" s="1"/>
+      <c r="N27" s="1"/>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A28" s="2">
         <v>38297</v>
       </c>
-      <c r="B28" s="1">
+      <c r="B28" s="2">
         <v>13392</v>
       </c>
-      <c r="C28" s="1">
+      <c r="C28" s="2">
         <v>114891</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" s="1">
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+      <c r="K28" s="1"/>
+      <c r="L28" s="1"/>
+      <c r="M28" s="1"/>
+      <c r="N28" s="1"/>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A29" s="2">
         <v>39766</v>
       </c>
-      <c r="B29" s="1">
+      <c r="B29" s="2">
         <v>13807</v>
       </c>
-      <c r="C29" s="1">
+      <c r="C29" s="2">
         <v>119298</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" s="1">
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+      <c r="K29" s="1"/>
+      <c r="L29" s="1"/>
+      <c r="M29" s="1"/>
+      <c r="N29" s="1"/>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A30" s="2">
         <v>41235</v>
       </c>
-      <c r="B30" s="1">
+      <c r="B30" s="2">
         <v>14264</v>
       </c>
-      <c r="C30" s="1">
+      <c r="C30" s="2">
         <v>123705</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" s="1">
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+      <c r="K30" s="1"/>
+      <c r="L30" s="1"/>
+      <c r="M30" s="1"/>
+      <c r="N30" s="1"/>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A31" s="2">
         <v>42704</v>
       </c>
-      <c r="B31" s="1">
+      <c r="B31" s="2">
         <v>14692</v>
       </c>
-      <c r="C31" s="1">
+      <c r="C31" s="2">
         <v>128112</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" s="1">
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1"/>
+      <c r="N31" s="1"/>
+      <c r="O31" s="1"/>
+      <c r="P31" s="1"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A32" s="2">
         <v>44173</v>
       </c>
-      <c r="B32" s="1">
+      <c r="B32" s="2">
         <v>15395</v>
       </c>
-      <c r="C32" s="1">
+      <c r="C32" s="2">
         <v>132519</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A33" s="1">
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+      <c r="O32" s="1"/>
+      <c r="P32" s="1"/>
+    </row>
+    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A33" s="2">
         <v>45642</v>
       </c>
-      <c r="B33" s="1">
+      <c r="B33" s="2">
         <v>15679</v>
       </c>
-      <c r="C33" s="1">
+      <c r="C33" s="2">
         <v>136926</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34" s="1">
+      <c r="D33" s="1"/>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="H33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
+      <c r="M33" s="1"/>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
+      <c r="P33" s="1"/>
+    </row>
+    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A34" s="2">
         <v>47111</v>
       </c>
-      <c r="B34" s="1">
+      <c r="B34" s="2">
         <v>16313</v>
       </c>
-      <c r="C34" s="1">
+      <c r="C34" s="2">
         <v>141333</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" s="1">
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="H34" s="1"/>
+      <c r="I34" s="1"/>
+      <c r="J34" s="1"/>
+      <c r="K34" s="1"/>
+      <c r="L34" s="1"/>
+      <c r="M34" s="1"/>
+      <c r="N34" s="1"/>
+      <c r="O34" s="1"/>
+      <c r="P34" s="1"/>
+    </row>
+    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A35" s="2">
         <v>48580</v>
       </c>
-      <c r="B35" s="1">
+      <c r="B35" s="2">
         <v>16786</v>
       </c>
-      <c r="C35" s="1">
+      <c r="C35" s="2">
         <v>145740</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A36" s="1">
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="H35" s="1"/>
+      <c r="I35" s="1"/>
+      <c r="J35" s="1"/>
+      <c r="K35" s="1"/>
+      <c r="L35" s="1"/>
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+      <c r="P35" s="1"/>
+    </row>
+    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A36" s="2">
         <v>50050</v>
       </c>
-      <c r="B36" s="1">
+      <c r="B36" s="2">
         <v>30042</v>
       </c>
-      <c r="C36" s="1">
+      <c r="C36" s="2">
         <v>150150</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" s="1">
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
+      <c r="F36" s="1"/>
+      <c r="G36" s="1"/>
+      <c r="H36" s="1"/>
+      <c r="I36" s="1"/>
+      <c r="J36" s="1"/>
+      <c r="K36" s="1"/>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1"/>
+      <c r="P36" s="1"/>
+    </row>
+    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A37" s="2">
         <v>51519</v>
       </c>
-      <c r="B37" s="1">
+      <c r="B37" s="2">
         <v>22745</v>
       </c>
-      <c r="C37" s="1">
+      <c r="C37" s="2">
         <v>154557</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" s="1">
+      <c r="D37" s="1"/>
+      <c r="E37" s="1"/>
+      <c r="F37" s="1"/>
+      <c r="G37" s="1"/>
+      <c r="H37" s="1"/>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
+      <c r="M37" s="1"/>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
+      <c r="P37" s="1"/>
+    </row>
+    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A38" s="2">
         <v>52988</v>
       </c>
-      <c r="B38" s="1">
+      <c r="B38" s="2">
         <v>18358</v>
       </c>
-      <c r="C38" s="1">
+      <c r="C38" s="2">
         <v>158964</v>
       </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A39" s="1">
+      <c r="D38" s="1"/>
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+      <c r="G38" s="1"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="1"/>
+      <c r="J38" s="1"/>
+      <c r="K38" s="1"/>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1"/>
+      <c r="N38" s="1"/>
+      <c r="O38" s="1"/>
+      <c r="P38" s="1"/>
+    </row>
+    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A39" s="2">
         <v>54457</v>
       </c>
-      <c r="B39" s="1">
+      <c r="B39" s="2">
         <v>19733</v>
       </c>
-      <c r="C39" s="1">
+      <c r="C39" s="2">
         <v>163371</v>
       </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" s="1">
+      <c r="D39" s="1"/>
+      <c r="E39" s="1"/>
+      <c r="F39" s="1"/>
+      <c r="G39" s="1"/>
+      <c r="H39" s="1"/>
+      <c r="I39" s="1"/>
+      <c r="J39" s="1"/>
+      <c r="K39" s="1"/>
+      <c r="L39" s="1"/>
+      <c r="M39" s="1"/>
+      <c r="N39" s="1"/>
+      <c r="O39" s="1"/>
+      <c r="P39" s="1"/>
+    </row>
+    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A40" s="2">
         <v>55926</v>
       </c>
-      <c r="B40" s="1">
+      <c r="B40" s="2">
         <v>19600</v>
       </c>
-      <c r="C40" s="1">
+      <c r="C40" s="2">
         <v>167778</v>
       </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A41" s="1">
+      <c r="D40" s="1"/>
+      <c r="E40" s="1"/>
+      <c r="F40" s="1"/>
+      <c r="G40" s="1"/>
+      <c r="H40" s="1"/>
+      <c r="I40" s="1"/>
+      <c r="J40" s="1"/>
+      <c r="K40" s="1"/>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1"/>
+      <c r="N40" s="1"/>
+      <c r="O40" s="1"/>
+      <c r="P40" s="1"/>
+    </row>
+    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A41" s="2">
         <v>57395</v>
       </c>
-      <c r="B41" s="1">
+      <c r="B41" s="2">
         <v>17994</v>
       </c>
-      <c r="C41" s="1">
+      <c r="C41" s="2">
         <v>172185</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" s="1">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A42" s="2">
         <v>58864</v>
       </c>
-      <c r="B42" s="1">
+      <c r="B42" s="2">
         <v>18363</v>
       </c>
-      <c r="C42" s="1">
+      <c r="C42" s="2">
         <v>176592</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" s="1">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A43" s="2">
         <v>60333</v>
       </c>
-      <c r="B43" s="1">
+      <c r="B43" s="2">
         <v>18950</v>
       </c>
-      <c r="C43" s="1">
+      <c r="C43" s="2">
         <v>180999</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A44" s="1">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A44" s="2">
         <v>61802</v>
       </c>
-      <c r="B44" s="1">
+      <c r="B44" s="2">
         <v>19500</v>
       </c>
-      <c r="C44" s="1">
+      <c r="C44" s="2">
         <v>185406</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A45" s="1">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A45" s="2">
         <v>63272</v>
       </c>
-      <c r="B45" s="1">
+      <c r="B45" s="2">
         <v>20190</v>
       </c>
-      <c r="C45" s="1">
+      <c r="C45" s="2">
         <v>189816</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A46" s="1">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A46" s="2">
         <v>64741</v>
       </c>
-      <c r="B46" s="1">
+      <c r="B46" s="2">
         <v>25458</v>
       </c>
-      <c r="C46" s="1">
+      <c r="C46" s="2">
         <v>194223</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A47" s="1">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A47" s="2">
         <v>66210</v>
       </c>
-      <c r="B47" s="1">
+      <c r="B47" s="2">
         <v>23253</v>
       </c>
-      <c r="C47" s="1">
+      <c r="C47" s="2">
         <v>198630</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A48" s="1">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A48" s="2">
         <v>67679</v>
       </c>
-      <c r="B48" s="1">
+      <c r="B48" s="2">
         <v>22215</v>
       </c>
-      <c r="C48" s="1">
+      <c r="C48" s="2">
         <v>203037</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A49" s="1">
+      <c r="A49" s="2">
         <v>69148</v>
       </c>
-      <c r="B49" s="1">
+      <c r="B49" s="2">
         <v>22877</v>
       </c>
-      <c r="C49" s="1">
+      <c r="C49" s="2">
         <v>207444</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A50" s="1">
+      <c r="A50" s="2">
         <v>70617</v>
       </c>
-      <c r="B50" s="1">
+      <c r="B50" s="2">
         <v>23048</v>
       </c>
-      <c r="C50" s="1">
+      <c r="C50" s="2">
         <v>211851</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A51" s="1">
+      <c r="A51" s="2">
         <v>72086</v>
       </c>
-      <c r="B51" s="1">
+      <c r="B51" s="2">
         <v>23961</v>
       </c>
-      <c r="C51" s="1">
+      <c r="C51" s="2">
         <v>216258</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A52" s="1">
+      <c r="A52" s="2">
         <v>73555</v>
       </c>
-      <c r="B52" s="1">
+      <c r="B52" s="2">
         <v>24341</v>
       </c>
-      <c r="C52" s="1">
+      <c r="C52" s="2">
         <v>220665</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A53" s="1">
+      <c r="A53" s="2">
         <v>75025</v>
       </c>
-      <c r="B53" s="1">
+      <c r="B53" s="2">
         <v>24937</v>
       </c>
-      <c r="C53" s="1">
+      <c r="C53" s="2">
         <v>225075</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A54" s="1">
+      <c r="A54" s="2">
         <v>76494</v>
       </c>
-      <c r="B54" s="1">
+      <c r="B54" s="2">
         <v>172370</v>
       </c>
-      <c r="C54" s="1">
+      <c r="C54" s="2">
         <v>229482</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A55" s="1">
+      <c r="A55" s="2">
         <v>77963</v>
       </c>
-      <c r="B55" s="1">
+      <c r="B55" s="2">
         <v>27258</v>
       </c>
-      <c r="C55" s="1">
+      <c r="C55" s="2">
         <v>233889</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A56" s="1">
+      <c r="A56" s="2">
         <v>79432</v>
       </c>
-      <c r="B56" s="1">
+      <c r="B56" s="2">
         <v>25424</v>
       </c>
-      <c r="C56" s="1">
+      <c r="C56" s="2">
         <v>238296</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A57" s="1">
+      <c r="A57" s="2">
         <v>80901</v>
       </c>
-      <c r="B57" s="1">
+      <c r="B57" s="2">
         <v>26998</v>
       </c>
-      <c r="C57" s="1">
+      <c r="C57" s="2">
         <v>242703</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A58" s="1">
+      <c r="A58" s="2">
         <v>82370</v>
       </c>
-      <c r="B58" s="1">
+      <c r="B58" s="2">
         <v>27243</v>
       </c>
-      <c r="C58" s="1">
+      <c r="C58" s="2">
         <v>247110</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A59" s="1">
+      <c r="A59" s="2">
         <v>83839</v>
       </c>
-      <c r="B59" s="1">
+      <c r="B59" s="2">
         <v>27716</v>
       </c>
-      <c r="C59" s="1">
+      <c r="C59" s="2">
         <v>251517</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A60" s="1">
+      <c r="A60" s="2">
         <v>85308</v>
       </c>
-      <c r="B60" s="1">
+      <c r="B60" s="2">
         <v>193583</v>
       </c>
-      <c r="C60" s="1">
+      <c r="C60" s="2">
         <v>255924</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A61" s="1">
+      <c r="A61" s="2">
         <v>86777</v>
       </c>
-      <c r="B61" s="1">
+      <c r="B61" s="2">
         <v>66551</v>
       </c>
-      <c r="C61" s="1">
+      <c r="C61" s="2">
         <v>260331</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A62" s="1">
+      <c r="A62" s="2">
         <v>88247</v>
       </c>
-      <c r="B62" s="1">
+      <c r="B62" s="2">
         <v>29963</v>
       </c>
-      <c r="C62" s="1">
+      <c r="C62" s="2">
         <v>264741</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A63" s="1">
+      <c r="A63" s="2">
         <v>89716</v>
       </c>
-      <c r="B63" s="1">
+      <c r="B63" s="2">
         <v>116323</v>
       </c>
-      <c r="C63" s="1">
+      <c r="C63" s="2">
         <v>269148</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A64" s="1">
+      <c r="A64" s="2">
         <v>91185</v>
       </c>
-      <c r="B64" s="1">
+      <c r="B64" s="2">
         <v>29332</v>
       </c>
-      <c r="C64" s="1">
+      <c r="C64" s="2">
         <v>273555</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A65" s="1">
+      <c r="A65" s="2">
         <v>92654</v>
       </c>
-      <c r="B65" s="1">
+      <c r="B65" s="2">
         <v>29897</v>
       </c>
-      <c r="C65" s="1">
+      <c r="C65" s="2">
         <v>277962</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A66" s="1">
+      <c r="A66" s="2">
         <v>94123</v>
       </c>
-      <c r="B66" s="1">
+      <c r="B66" s="2">
         <v>183158</v>
       </c>
-      <c r="C66" s="1">
+      <c r="C66" s="2">
         <v>282369</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A67" s="1">
+      <c r="A67" s="2">
         <v>95592</v>
       </c>
-      <c r="B67" s="1">
+      <c r="B67" s="2">
         <v>37006</v>
       </c>
-      <c r="C67" s="1">
+      <c r="C67" s="2">
         <v>286776</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A68" s="1">
+      <c r="A68" s="2">
         <v>97061</v>
       </c>
-      <c r="B68" s="1">
+      <c r="B68" s="2">
         <v>41123</v>
       </c>
-      <c r="C68" s="1">
+      <c r="C68" s="2">
         <v>291183</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A69" s="1">
+      <c r="A69" s="2">
         <v>98530</v>
       </c>
-      <c r="B69" s="1">
+      <c r="B69" s="2">
         <v>30365</v>
       </c>
-      <c r="C69" s="1">
+      <c r="C69" s="2">
         <v>295590</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A70" s="1">
+      <c r="A70" s="2">
         <v>100000</v>
       </c>
-      <c r="B70" s="1">
+      <c r="B70" s="2">
         <v>32247</v>
       </c>
-      <c r="C70" s="1">
+      <c r="C70" s="2">
         <v>300000</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>